--- a/csv/model/CIMS_base/formula_CIMS_base_CIMS.xlsx
+++ b/csv/model/CIMS_base/formula_CIMS_base_CIMS.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
+  <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="3624" yWindow="2148" windowWidth="17280" windowHeight="8880" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
@@ -12,7 +12,7 @@
     <externalReference r:id="rId2"/>
   </externalReferences>
   <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1" calcOnSave="0"/>
 </workbook>
 </file>
 
@@ -501,12 +501,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
+  <sheetPr codeName="Sheet1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:X13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
       <c r="B1" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Service provided</t>
+          <t>service_provide</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -660,7 +660,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Competition type</t>
+          <t>competition</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -687,7 +687,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Currency</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -763,7 +763,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Emissions_GWP</t>
+          <t>emissions_gwp</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Emissions_GWP</t>
+          <t>emissions_gwp</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -925,7 +925,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Emissions_GWP</t>
+          <t>emissions_gwp</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1005,7 +1005,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tax_foresight</t>
+          <t>tax_foresight</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1077,7 +1077,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Retrofit_heterogeneity</t>
+          <t>retrofit_heterogeneity</t>
         </is>
       </c>
       <c r="M10" t="n">
@@ -1142,7 +1142,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Retrofit_existing_max</t>
+          <t>retrofit_existing_max</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Service requested</t>
+          <t>service_request</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1282,7 +1282,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Service requested</t>
+          <t>service_request</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
